--- a/data/kanji1.xlsx
+++ b/data/kanji1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mint_\Documents\勉強アプリ\漢字ドリル中１\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FC66C8-C392-48BD-8ED4-179D5A762C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DAF0F2-6735-4C87-AF13-AA5D84728335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="漢字" sheetId="1" r:id="rId1"/>
     <sheet name="慣用句" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="部首" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">漢字!$A$1:$F$325</definedName>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="844">
   <si>
     <t>No</t>
   </si>
@@ -2317,6 +2317,246 @@
   </si>
   <si>
     <t>同じことを何度も繰り返し、注意やアドバイスを与える。</t>
+  </si>
+  <si>
+    <t>部首</t>
+  </si>
+  <si>
+    <t>猫・犬・独に共通する部首は？</t>
+  </si>
+  <si>
+    <t>けものへん（犭）・動物や獣に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>橋・板・植に共通する部首は？</t>
+  </si>
+  <si>
+    <t>きへん（木）・木や植物、木材に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>話・読・計に共通する部首は？</t>
+  </si>
+  <si>
+    <t>ごんべん（訁）・言葉や話すこと、伝えることに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>鉄・銀・銅に共通する部首は？</t>
+  </si>
+  <si>
+    <t>かねへん（釒）・金属や金属製品に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>紙・級・終に共通する部首は？</t>
+  </si>
+  <si>
+    <t>いとへん（糹）・糸や布、結ぶことに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>花・草・葉に共通する部首は？</t>
+  </si>
+  <si>
+    <t>くさかんむり（艹）・草や植物に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>箱・筆・第に共通する部首は？</t>
+  </si>
+  <si>
+    <t>たけかんむり（⺮）・竹や竹製品に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>坂・城・境に共通する部首は？</t>
+  </si>
+  <si>
+    <t>つちへん（土）・土地や地面、建物に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>研・破・碑に共通する部首は？</t>
+  </si>
+  <si>
+    <t>いしへん（石）・石や岩、鉱物に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>★★☆</t>
+  </si>
+  <si>
+    <t>唱・呼・吸に共通する部首は？</t>
+  </si>
+  <si>
+    <t>くちへん（口）・口や話すこと、声や呼吸に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>海・湖・泳に共通する部首は？</t>
+  </si>
+  <si>
+    <t>さんずい（⺡）・水や川、液体に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>病・痛・疲に共通する部首は？</t>
+  </si>
+  <si>
+    <t>やまいだれ（疒）・病気や体の不調に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>持・投・拾に共通する部首は？</t>
+  </si>
+  <si>
+    <t>てへん（扌）・手を使う動作や行為に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>情・怖・忙に共通する部首は？</t>
+  </si>
+  <si>
+    <t>りっしんべん（忄）・心や感情に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>信・作・仕に共通する部首は？</t>
+  </si>
+  <si>
+    <t>にんべん（⺅）・人や人の動作・状態に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>進・返・迷に共通する部首は？</t>
+  </si>
+  <si>
+    <t>しんにょう（⻌）・道を進むことや移動に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>神・福・祝に共通する部首は？</t>
+  </si>
+  <si>
+    <t>しめすへん（礻）・神や祭り、祈りに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>初・被・複に共通する部首は？</t>
+  </si>
+  <si>
+    <t>ころもへん（衤）・衣服や布に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>財・貧・買に共通する部首は？</t>
+  </si>
+  <si>
+    <t>かい・かいへん（貝）・財産やお金、売買に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>雪・雲・霜に共通する部首は？</t>
+  </si>
+  <si>
+    <t>あめかんむり（⻗）・雨や天候に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>冷・凍・凄に共通する部首は？</t>
+  </si>
+  <si>
+    <t>にすい（冫）・氷や冷たさに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>家・室・守に共通する部首は？</t>
+  </si>
+  <si>
+    <t>うかんむり（宀）・家や建物、屋根の下に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>空・究・窓に共通する部首は？</t>
+  </si>
+  <si>
+    <t>あなかんむり（穴）・穴や空間に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>院・防・階に共通する部首は？</t>
+  </si>
+  <si>
+    <t>こざとへん（⻖）・丘や階段、土地の高低に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>都・郡・邦に共通する部首は？</t>
+  </si>
+  <si>
+    <t>おおざと（⻏）・国や地域、村や都市に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>行・律・徒に共通する部首は？</t>
+  </si>
+  <si>
+    <t>ぎょうにんべん（彳）・歩くことや道、行動に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>病・症・疲に共通する部首は？</t>
+  </si>
+  <si>
+    <t>顔・頭・額に共通する部首は？</t>
+  </si>
+  <si>
+    <t>おおがい（頁）・頭や顔など頭部に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>美・義・群に共通する部首は？</t>
+  </si>
+  <si>
+    <t>ひつじ・ひつじへん（羊）・羊や美しさ、善さに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>戦・成・戒に共通する部首は？</t>
+  </si>
+  <si>
+    <t>ほこづくり（戈）・武器や戦いに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>姉・妹・婦に共通する部首は？</t>
+  </si>
+  <si>
+    <t>おんなへん（女）・女性や女性に関係することを表す漢字に使われる。</t>
+  </si>
+  <si>
+    <t>想・意・忍に共通する部首は？</t>
+  </si>
+  <si>
+    <t>こころ（心）・心や感情、考えに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>聞・聖・職に共通する部首は？</t>
+  </si>
+  <si>
+    <t>みみへん（耳）・耳や聞くことに関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>むしへん（虫）・虫や小さな生き物に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>鮮・鯨・鯉に共通する部首は？</t>
+  </si>
+  <si>
+    <t>さかなへん（魚）・魚や水中の生き物に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>鳴・鶴・鳩に共通する部首は？</t>
+  </si>
+  <si>
+    <t>とりへん（鳥）・鳥や鳥類に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>駅・駐・騎に共通する部首は？</t>
+  </si>
+  <si>
+    <t>うまへん（馬）・馬や馬に関係することを表す漢字に使われる。</t>
+  </si>
+  <si>
+    <t>飯・飲・館に共通する部首は？</t>
+  </si>
+  <si>
+    <t>しょくへん（飠・食）・食べることや飲食に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>軽・転・輪に共通する部首は？</t>
+  </si>
+  <si>
+    <t>くるまへん（車）・車や乗り物、車輪に関係する漢字に使われる。</t>
+  </si>
+  <si>
+    <t>蚊・蛇・蜂に共通する部首は？</t>
+  </si>
+  <si>
+    <t>岩・砂・碑に共通する部首は？</t>
   </si>
 </sst>
 </file>
@@ -8665,10 +8905,719 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF70D5C-DFA3-403A-8BD8-A1D98475FBDC}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EA25FC-7E4C-448F-9FD9-94B9CF959C64}">
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D3" t="s">
+        <v>789</v>
+      </c>
+      <c r="E3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D4" t="s">
+        <v>791</v>
+      </c>
+      <c r="E4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>764</v>
+      </c>
+      <c r="C5" t="s">
+        <v>792</v>
+      </c>
+      <c r="D5" t="s">
+        <v>793</v>
+      </c>
+      <c r="E5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>764</v>
+      </c>
+      <c r="C6" t="s">
+        <v>794</v>
+      </c>
+      <c r="D6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E6" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>764</v>
+      </c>
+      <c r="C7" t="s">
+        <v>796</v>
+      </c>
+      <c r="D7" t="s">
+        <v>797</v>
+      </c>
+      <c r="E7" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>764</v>
+      </c>
+      <c r="C8" t="s">
+        <v>798</v>
+      </c>
+      <c r="D8" t="s">
+        <v>799</v>
+      </c>
+      <c r="E8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>764</v>
+      </c>
+      <c r="C9" t="s">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>801</v>
+      </c>
+      <c r="E9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" t="s">
+        <v>802</v>
+      </c>
+      <c r="D10" t="s">
+        <v>803</v>
+      </c>
+      <c r="E10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>764</v>
+      </c>
+      <c r="C11" t="s">
+        <v>804</v>
+      </c>
+      <c r="D11" t="s">
+        <v>805</v>
+      </c>
+      <c r="E11" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C12" t="s">
+        <v>806</v>
+      </c>
+      <c r="D12" t="s">
+        <v>807</v>
+      </c>
+      <c r="E12" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>764</v>
+      </c>
+      <c r="C13" t="s">
+        <v>808</v>
+      </c>
+      <c r="D13" t="s">
+        <v>809</v>
+      </c>
+      <c r="E13" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>764</v>
+      </c>
+      <c r="C14" t="s">
+        <v>810</v>
+      </c>
+      <c r="D14" t="s">
+        <v>811</v>
+      </c>
+      <c r="E14" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>764</v>
+      </c>
+      <c r="C15" t="s">
+        <v>812</v>
+      </c>
+      <c r="D15" t="s">
+        <v>813</v>
+      </c>
+      <c r="E15" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>764</v>
+      </c>
+      <c r="C16" t="s">
+        <v>814</v>
+      </c>
+      <c r="D16" t="s">
+        <v>815</v>
+      </c>
+      <c r="E16" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>764</v>
+      </c>
+      <c r="C17" t="s">
+        <v>816</v>
+      </c>
+      <c r="D17" t="s">
+        <v>817</v>
+      </c>
+      <c r="E17" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>764</v>
+      </c>
+      <c r="C18" t="s">
+        <v>818</v>
+      </c>
+      <c r="D18" t="s">
+        <v>789</v>
+      </c>
+      <c r="E18" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>764</v>
+      </c>
+      <c r="C19" t="s">
+        <v>819</v>
+      </c>
+      <c r="D19" t="s">
+        <v>820</v>
+      </c>
+      <c r="E19" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>764</v>
+      </c>
+      <c r="C20" t="s">
+        <v>821</v>
+      </c>
+      <c r="D20" t="s">
+        <v>822</v>
+      </c>
+      <c r="E20" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>764</v>
+      </c>
+      <c r="C21" t="s">
+        <v>823</v>
+      </c>
+      <c r="D21" t="s">
+        <v>824</v>
+      </c>
+      <c r="E21" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>764</v>
+      </c>
+      <c r="C22" t="s">
+        <v>765</v>
+      </c>
+      <c r="D22" t="s">
+        <v>766</v>
+      </c>
+      <c r="E22" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>764</v>
+      </c>
+      <c r="C23" t="s">
+        <v>767</v>
+      </c>
+      <c r="D23" t="s">
+        <v>768</v>
+      </c>
+      <c r="E23" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>764</v>
+      </c>
+      <c r="C24" t="s">
+        <v>769</v>
+      </c>
+      <c r="D24" t="s">
+        <v>770</v>
+      </c>
+      <c r="E24" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>764</v>
+      </c>
+      <c r="C25" t="s">
+        <v>771</v>
+      </c>
+      <c r="D25" t="s">
+        <v>772</v>
+      </c>
+      <c r="E25" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>764</v>
+      </c>
+      <c r="C26" t="s">
+        <v>773</v>
+      </c>
+      <c r="D26" t="s">
+        <v>774</v>
+      </c>
+      <c r="E26" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>764</v>
+      </c>
+      <c r="C27" t="s">
+        <v>775</v>
+      </c>
+      <c r="D27" t="s">
+        <v>776</v>
+      </c>
+      <c r="E27" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>764</v>
+      </c>
+      <c r="C28" t="s">
+        <v>777</v>
+      </c>
+      <c r="D28" t="s">
+        <v>778</v>
+      </c>
+      <c r="E28" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>764</v>
+      </c>
+      <c r="C29" t="s">
+        <v>779</v>
+      </c>
+      <c r="D29" t="s">
+        <v>780</v>
+      </c>
+      <c r="E29" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>764</v>
+      </c>
+      <c r="C30" t="s">
+        <v>781</v>
+      </c>
+      <c r="D30" t="s">
+        <v>782</v>
+      </c>
+      <c r="E30" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>764</v>
+      </c>
+      <c r="C31" t="s">
+        <v>784</v>
+      </c>
+      <c r="D31" t="s">
+        <v>785</v>
+      </c>
+      <c r="E31" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>764</v>
+      </c>
+      <c r="C32" t="s">
+        <v>825</v>
+      </c>
+      <c r="D32" t="s">
+        <v>826</v>
+      </c>
+      <c r="E32" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>764</v>
+      </c>
+      <c r="C33" t="s">
+        <v>827</v>
+      </c>
+      <c r="D33" t="s">
+        <v>828</v>
+      </c>
+      <c r="E33" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>764</v>
+      </c>
+      <c r="C34" t="s">
+        <v>829</v>
+      </c>
+      <c r="D34" t="s">
+        <v>830</v>
+      </c>
+      <c r="E34" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>764</v>
+      </c>
+      <c r="C35" t="s">
+        <v>842</v>
+      </c>
+      <c r="D35" t="s">
+        <v>831</v>
+      </c>
+      <c r="E35" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>764</v>
+      </c>
+      <c r="C36" t="s">
+        <v>832</v>
+      </c>
+      <c r="D36" t="s">
+        <v>833</v>
+      </c>
+      <c r="E36" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>764</v>
+      </c>
+      <c r="C37" t="s">
+        <v>834</v>
+      </c>
+      <c r="D37" t="s">
+        <v>835</v>
+      </c>
+      <c r="E37" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>764</v>
+      </c>
+      <c r="C38" t="s">
+        <v>836</v>
+      </c>
+      <c r="D38" t="s">
+        <v>837</v>
+      </c>
+      <c r="E38" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>764</v>
+      </c>
+      <c r="C39" t="s">
+        <v>838</v>
+      </c>
+      <c r="D39" t="s">
+        <v>839</v>
+      </c>
+      <c r="E39" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>764</v>
+      </c>
+      <c r="C40" t="s">
+        <v>840</v>
+      </c>
+      <c r="D40" t="s">
+        <v>841</v>
+      </c>
+      <c r="E40" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>764</v>
+      </c>
+      <c r="C41" t="s">
+        <v>843</v>
+      </c>
+      <c r="D41" t="s">
+        <v>782</v>
+      </c>
+      <c r="E41" t="s">
+        <v>740</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
